--- a/docs/signup-template.xlsx
+++ b/docs/signup-template.xlsx
@@ -11,8 +11,8 @@
     <sheet name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'참가신청서'!$A$1:$O$65</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$O$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'참가신청서'!$A$1:$M$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$M$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -135,11 +135,44 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,9 +239,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -580,24 +615,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="4.5" customWidth="1" min="2" max="2"/>
-    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="4.5" customWidth="1" min="4" max="4"/>
-    <col width="5.5" customWidth="1" min="5" max="5"/>
-    <col width="7.5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="5.5" customWidth="1" min="6" max="6"/>
     <col width="5.5" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9.5" customWidth="1" min="10" max="10"/>
-    <col width="4.5" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="7.5" customWidth="1" min="13" max="13"/>
-    <col width="8.5" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="4.5" customWidth="1" min="10" max="10"/>
+    <col width="7.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -607,14 +640,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="15.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>노란 칸만 입력 · 대표/팀 명단에는 개인전 명단과 똑같은 이름 · 챔프전은 1조만 · 사이드·챔프전 참가는 O 표시 · 수량·금액은 자동 계산</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="15.5" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>클럽명</t>
@@ -623,8 +656,7 @@
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>지역명</t>
         </is>
@@ -636,13 +668,10 @@
           <t>연락처</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="5" t="n"/>
+      <c r="L3" s="4" t="n"/>
       <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
+    </row>
+    <row r="4" ht="15.5" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>개인전</t>
@@ -663,19 +692,17 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>2조</t>
         </is>
       </c>
+      <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+    </row>
+    <row r="5" ht="15.5" customHeight="1">
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -694,56 +721,46 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>시니어핸디</t>
+          <t>사이드</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
+          <t>챔프전</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>사이드</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>챔프전</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>핸디</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>시니어핸디</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>사이드</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
+    </row>
+    <row r="6" ht="15.5" customHeight="1">
       <c r="B6" s="10" t="n">
         <v>1</v>
       </c>
@@ -752,16 +769,14 @@
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="11" t="n"/>
       <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
+      <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
+      <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
       <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+      <c r="M6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="15.5" customHeight="1">
       <c r="B7" s="10" t="n">
         <v>2</v>
       </c>
@@ -770,16 +785,14 @@
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="11" t="n"/>
       <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
+      <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+      <c r="M7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="15.5" customHeight="1">
       <c r="B8" s="10" t="n">
         <v>3</v>
       </c>
@@ -788,16 +801,14 @@
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
+      <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
+      <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
       <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
+      <c r="M8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="15.5" customHeight="1">
       <c r="B9" s="10" t="n">
         <v>4</v>
       </c>
@@ -806,16 +817,14 @@
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
+      <c r="J9" s="11" t="n"/>
       <c r="K9" s="11" t="n"/>
       <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+      <c r="M9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="15.5" customHeight="1">
       <c r="B10" s="10" t="n">
         <v>5</v>
       </c>
@@ -824,16 +833,14 @@
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
+      <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="J10" s="11" t="n"/>
       <c r="K10" s="11" t="n"/>
       <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+      <c r="M10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="15.5" customHeight="1">
       <c r="B11" s="10" t="n">
         <v>6</v>
       </c>
@@ -842,16 +849,14 @@
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
+      <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="J11" s="11" t="n"/>
       <c r="K11" s="11" t="n"/>
       <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+      <c r="M11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="15.5" customHeight="1">
       <c r="B12" s="10" t="n">
         <v>7</v>
       </c>
@@ -860,16 +865,14 @@
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="J12" s="11" t="n"/>
       <c r="K12" s="11" t="n"/>
       <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
+      <c r="M12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="15.5" customHeight="1">
       <c r="B13" s="10" t="n">
         <v>8</v>
       </c>
@@ -878,16 +881,14 @@
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
+      <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="11" t="n"/>
       <c r="K13" s="11" t="n"/>
       <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+      <c r="M13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="15.5" customHeight="1">
       <c r="B14" s="10" t="n">
         <v>9</v>
       </c>
@@ -896,16 +897,14 @@
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
+      <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="J14" s="11" t="n"/>
       <c r="K14" s="11" t="n"/>
       <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+      <c r="M14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="15.5" customHeight="1">
       <c r="B15" s="10" t="n">
         <v>10</v>
       </c>
@@ -914,16 +913,14 @@
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="11" t="n"/>
       <c r="K15" s="11" t="n"/>
       <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+      <c r="M15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="15.5" customHeight="1">
       <c r="B16" s="10" t="n">
         <v>11</v>
       </c>
@@ -932,16 +929,14 @@
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="J16" s="11" t="n"/>
       <c r="K16" s="11" t="n"/>
       <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+      <c r="M16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="15.5" customHeight="1">
       <c r="B17" s="10" t="n">
         <v>12</v>
       </c>
@@ -950,16 +945,14 @@
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="11" t="n"/>
       <c r="K17" s="11" t="n"/>
       <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+      <c r="M17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="15.5" customHeight="1">
       <c r="B18" s="10" t="n">
         <v>13</v>
       </c>
@@ -968,16 +961,14 @@
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+      <c r="M18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="15.5" customHeight="1">
       <c r="B19" s="10" t="n">
         <v>14</v>
       </c>
@@ -986,16 +977,14 @@
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
+      <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
+      <c r="J19" s="11" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+      <c r="M19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="15.5" customHeight="1">
       <c r="B20" s="10" t="n">
         <v>15</v>
       </c>
@@ -1004,16 +993,14 @@
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
+      <c r="J20" s="11" t="n"/>
       <c r="K20" s="11" t="n"/>
       <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+      <c r="M20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="15.5" customHeight="1">
       <c r="B21" s="10" t="n">
         <v>16</v>
       </c>
@@ -1022,16 +1009,14 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="11" t="n"/>
       <c r="K21" s="11" t="n"/>
       <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+      <c r="M21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="15.5" customHeight="1">
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1043,19 +1028,17 @@
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>참가비 내역 (자동 계산)</t>
         </is>
       </c>
+      <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+    </row>
+    <row r="23" ht="15.5" customHeight="1">
       <c r="B23" s="10" t="n">
         <v>1</v>
       </c>
@@ -1063,33 +1046,31 @@
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="K23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="O23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+    </row>
+    <row r="24" ht="15.5" customHeight="1">
       <c r="B24" s="10" t="n">
         <v>2</v>
       </c>
@@ -1097,29 +1078,27 @@
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>개인전 참가비</t>
         </is>
       </c>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="16" t="n">
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="16" t="n">
         <v>35000</v>
       </c>
-      <c r="M24" s="17">
-        <f>COUNTA(C6:C21)+COUNTA(J6:J21)+COUNTA(C23:C34)</f>
+      <c r="L24" s="17">
+        <f>COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34)</f>
         <v/>
       </c>
-      <c r="N24" s="18">
-        <f>L24*M24</f>
+      <c r="M24" s="18">
+        <f>K24*L24</f>
         <v/>
       </c>
-      <c r="O24" s="15" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+    </row>
+    <row r="25" ht="15.5" customHeight="1">
       <c r="B25" s="10" t="n">
         <v>3</v>
       </c>
@@ -1127,29 +1106,27 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>챔프전 참가비</t>
         </is>
       </c>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="16" t="n">
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="M25" s="17">
-        <f>COUNTIF(H6:H21,"O")</f>
+      <c r="L25" s="17">
+        <f>COUNTIF(G6:G21,"O")</f>
         <v/>
       </c>
-      <c r="N25" s="18">
-        <f>L25*M25</f>
+      <c r="M25" s="18">
+        <f>K25*L25</f>
         <v/>
       </c>
-      <c r="O25" s="15" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+    </row>
+    <row r="26" ht="15.5" customHeight="1">
       <c r="B26" s="10" t="n">
         <v>4</v>
       </c>
@@ -1157,29 +1134,27 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>사이드 참가비</t>
         </is>
       </c>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="16" t="n">
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="M26" s="17">
-        <f>COUNTIF(G6:G21,"O")+COUNTIF(N6:N21,"O")+COUNTIF(G23:G34,"O")</f>
+      <c r="L26" s="17">
+        <f>COUNTIF(F6:F21,"O")+COUNTIF(L6:L21,"O")+COUNTIF(F23:F34,"O")</f>
         <v/>
       </c>
-      <c r="N26" s="18">
-        <f>L26*M26</f>
+      <c r="M26" s="18">
+        <f>K26*L26</f>
         <v/>
       </c>
-      <c r="O26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+    </row>
+    <row r="27" ht="15.5" customHeight="1">
       <c r="B27" s="10" t="n">
         <v>5</v>
       </c>
@@ -1187,28 +1162,26 @@
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>클럽 참가비</t>
         </is>
       </c>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="16" t="n">
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="16" t="n">
         <v>110000</v>
       </c>
-      <c r="M27" s="17" t="n">
+      <c r="L27" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="18">
-        <f>L27*M27</f>
+      <c r="M27" s="18">
+        <f>K27*L27</f>
         <v/>
       </c>
-      <c r="O27" s="15" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+    </row>
+    <row r="28" ht="15.5" customHeight="1">
       <c r="B28" s="10" t="n">
         <v>6</v>
       </c>
@@ -1216,28 +1189,26 @@
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>클럽 찬조금</t>
         </is>
       </c>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="16" t="n">
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="16" t="n">
         <v>50000</v>
       </c>
-      <c r="M28" s="17" t="n">
+      <c r="L28" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="18">
-        <f>L28*M28</f>
+      <c r="M28" s="18">
+        <f>K28*L28</f>
         <v/>
       </c>
-      <c r="O28" s="15" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+    </row>
+    <row r="29" ht="15.5" customHeight="1">
       <c r="B29" s="10" t="n">
         <v>7</v>
       </c>
@@ -1245,23 +1216,21 @@
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>개인 찬조</t>
         </is>
       </c>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="16" t="n">
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="15" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+    </row>
+    <row r="30" ht="15.5" customHeight="1">
       <c r="B30" s="10" t="n">
         <v>8</v>
       </c>
@@ -1269,24 +1238,22 @@
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
+      <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="20">
-        <f>SUM(N24:N29)</f>
+      <c r="M30" s="20">
+        <f>SUM(M24:M29)</f>
         <v/>
       </c>
-      <c r="O30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+    </row>
+    <row r="31" ht="15.5" customHeight="1">
       <c r="B31" s="10" t="n">
         <v>9</v>
       </c>
@@ -1294,16 +1261,15 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당(여성 15 등), 시니어핸디는 별도 칸(합산). 프로 감점 등은 핸디에 음수로 적고 비고에 표시.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당 합계(여성 15, 시니어 1~5, 프로 감점 등 합산)로 적고 내역은 비고에.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.5" customHeight="1">
       <c r="B32" s="10" t="n">
         <v>10</v>
       </c>
@@ -1311,11 +1277,10 @@
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="15.5" customHeight="1">
       <c r="B33" s="10" t="n">
         <v>11</v>
       </c>
@@ -1323,11 +1288,10 @@
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="15.5" customHeight="1">
       <c r="B34" s="10" t="n">
         <v>12</v>
       </c>
@@ -1335,13 +1299,12 @@
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="15.5" customHeight="1">
       <c r="B35" s="22">
-        <f>"총 인원 "&amp;(COUNTA(C6:C21)+COUNTA(J6:J21)+COUNTA(C23:C34))&amp;"명 (1조 "&amp;COUNTA(C6:C21)&amp;"명, 2조 "&amp;COUNTA(J6:J21)&amp;"명, 3조 "&amp;COUNTA(C23:C34)&amp;"명, 챔프전 "&amp;M25&amp;"명, 사이드 "&amp;M26&amp;"명)"</f>
+        <f>"총 인원 "&amp;(COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34))&amp;"명 (1조 "&amp;COUNTA(C6:C21)&amp;"명, 2조 "&amp;COUNTA(I6:I21)&amp;"명, 3조 "&amp;COUNTA(C23:C34)&amp;"명, 챔프전 "&amp;L25&amp;"명, 사이드 "&amp;L26&amp;"명)"</f>
         <v/>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -1355,42 +1318,127 @@
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
+    </row>
+    <row r="36" ht="15.5" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
           <t>3인조</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>선수1</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>선수2</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>선수3</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="15.5" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>지역 대표 3명</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>3인조: 지역 대표 3명 (개인전 합계로 지역 순위 포인트)   스카치: 남 1 + 여 1   베이커: 3명</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="15" t="n"/>
-      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="11" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15.5" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>스카치</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>선수1</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>선수2</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="15.5" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>남1 + 여1
+2게임</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
@@ -1398,285 +1446,333 @@
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="11" t="n"/>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>팀 순서대로 번호가 붙습니다 (지역명1, 지역명2 …). 핸디(베이커 여성 +3/+5 등)는 대회에서 적용합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="15" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="15.5" customHeight="1">
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="11" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="15" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="15.5" customHeight="1">
+      <c r="A41" s="24" t="n"/>
       <c r="B41" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="15" t="n"/>
-      <c r="B42" s="15" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="15.5" customHeight="1">
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="11" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="15" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="15.5" customHeight="1">
+      <c r="A43" s="25" t="n"/>
       <c r="B43" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="15" t="n"/>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="11" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="15" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="15.5" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>베이커</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>선수1</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>선수2</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>선수3</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="15.5" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>3인
+2게임</t>
+        </is>
+      </c>
       <c r="B45" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="15" t="n"/>
-      <c r="B46" s="15" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="15.5" customHeight="1">
+      <c r="A46" s="24" t="n"/>
+      <c r="B46" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="15" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="15.5" customHeight="1">
+      <c r="A47" s="24" t="n"/>
       <c r="B47" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="15" t="n"/>
-      <c r="B48" s="15" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="15.5" customHeight="1">
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>베이커</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="15.5" customHeight="1">
+      <c r="A49" s="25" t="n"/>
       <c r="B49" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="11" t="n"/>
-      <c r="F49" s="23" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="15" t="n"/>
-      <c r="B50" s="15" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="11" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="15" t="n"/>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="11" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="15" t="n"/>
-      <c r="B52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="11" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="15" t="n"/>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="15" t="n"/>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="11" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="15" t="n"/>
-      <c r="B55" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="15" t="n"/>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="11" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="15" t="n"/>
-      <c r="B57" s="15" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="11" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="15" t="n"/>
-      <c r="B58" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="11" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="15" t="n"/>
-      <c r="B59" s="15" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="11" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="15" t="n"/>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="11" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="15" t="n"/>
-      <c r="B61" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="11" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="15" t="n"/>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="11" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="15" t="n"/>
-      <c r="B63" s="15" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="11" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="15.5" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
-      <c r="C64" s="20">
-        <f>N30</f>
+      <c r="C50" s="20">
+        <f>M30</f>
         <v/>
       </c>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="24" t="inlineStr">
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>입금계좌 : (대회 공지의 계좌)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="25" t="inlineStr">
+    <row r="51" ht="15.5" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>위와 같이 제46회 네이버 볼링 동호회 서울 전국대회 참가를 신청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1"/>
-    <row r="68" ht="15" customHeight="1"/>
-    <row r="69" ht="15" customHeight="1"/>
+    <row r="52" ht="15.5" customHeight="1"/>
+    <row r="53" ht="15.5" customHeight="1"/>
+    <row r="54" ht="15.5" customHeight="1"/>
+    <row r="55" ht="15.5" customHeight="1"/>
+    <row r="56" ht="15.5" customHeight="1"/>
+    <row r="57" ht="15.5" customHeight="1"/>
+    <row r="58" ht="15.5" customHeight="1"/>
+    <row r="59" ht="15.5" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="50">
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="A65:O65"/>
-    <mergeCell ref="B35:O35"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="F39:O48"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="A49:A63"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A39:A48"/>
-    <mergeCell ref="J24:K24"/>
+  <mergeCells count="58">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="I25:J25"/>
     <mergeCell ref="A4:A34"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="F64:O64"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E40:F40"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="J31:O33"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="I31:M34"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="B35:M35"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="A37"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="F36:O38"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="F49:O63"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation sqref="D6:D21 D23:D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="D6:D21 D23:D34 J6:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F21 F23:F34 G6:G21 L6:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D37 G37 I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:G21 G23:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N6:N21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H6:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D36:D38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D39:D43 G39:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D39:D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"남,여"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D49:D63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D45:D49 G45:G49 I45:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1692,24 +1788,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="4.5" customWidth="1" min="2" max="2"/>
-    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="4.5" customWidth="1" min="4" max="4"/>
-    <col width="5.5" customWidth="1" min="5" max="5"/>
-    <col width="7.5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="5.5" customWidth="1" min="6" max="6"/>
     <col width="5.5" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9.5" customWidth="1" min="10" max="10"/>
-    <col width="4.5" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="7.5" customWidth="1" min="13" max="13"/>
-    <col width="8.5" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="4.5" customWidth="1" min="10" max="10"/>
+    <col width="7.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1719,14 +1813,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="15.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>노란 칸만 입력 · 대표/팀 명단에는 개인전 명단과 똑같은 이름 · 챔프전은 1조만 · 사이드·챔프전 참가는 O 표시 · 수량·금액은 자동 계산</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="15.5" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>클럽명</t>
@@ -1739,8 +1833,7 @@
       </c>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>지역명</t>
         </is>
@@ -1756,17 +1849,14 @@
           <t>연락처</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>010-0000-0000 (총무 홍길동)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
+    </row>
+    <row r="4" ht="15.5" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>개인전</t>
@@ -1787,19 +1877,17 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>2조</t>
         </is>
       </c>
+      <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+    </row>
+    <row r="5" ht="15.5" customHeight="1">
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -1818,56 +1906,46 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>시니어핸디</t>
+          <t>사이드</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
+          <t>챔프전</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>사이드</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>챔프전</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>핸디</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>시니어핸디</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>사이드</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
+    </row>
+    <row r="6" ht="15.5" customHeight="1">
       <c r="B6" s="10" t="n">
         <v>1</v>
       </c>
@@ -1882,46 +1960,42 @@
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>이순자</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>이순자</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>시니어 66세</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>시니어 66세 (15+5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.5" customHeight="1">
       <c r="B7" s="10" t="n">
         <v>2</v>
       </c>
@@ -1938,40 +2012,38 @@
       <c r="E7" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>최민수</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>남</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>프로 (게임당 -7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>프로</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.5" customHeight="1">
       <c r="B8" s="10" t="n">
         <v>3</v>
       </c>
@@ -1985,33 +2057,31 @@
           <t>남</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n">
+      <c r="E8" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>시니어 63세</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
       <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
+      <c r="M8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="15.5" customHeight="1">
       <c r="B9" s="10" t="n">
         <v>4</v>
       </c>
@@ -2020,16 +2090,14 @@
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
+      <c r="J9" s="11" t="n"/>
       <c r="K9" s="11" t="n"/>
       <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+      <c r="M9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="15.5" customHeight="1">
       <c r="B10" s="10" t="n">
         <v>5</v>
       </c>
@@ -2038,16 +2106,14 @@
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
+      <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="J10" s="11" t="n"/>
       <c r="K10" s="11" t="n"/>
       <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+      <c r="M10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="15.5" customHeight="1">
       <c r="B11" s="10" t="n">
         <v>6</v>
       </c>
@@ -2056,16 +2122,14 @@
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
+      <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="J11" s="11" t="n"/>
       <c r="K11" s="11" t="n"/>
       <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+      <c r="M11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="15.5" customHeight="1">
       <c r="B12" s="10" t="n">
         <v>7</v>
       </c>
@@ -2074,16 +2138,14 @@
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="J12" s="11" t="n"/>
       <c r="K12" s="11" t="n"/>
       <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
+      <c r="M12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="15.5" customHeight="1">
       <c r="B13" s="10" t="n">
         <v>8</v>
       </c>
@@ -2092,16 +2154,14 @@
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
+      <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="11" t="n"/>
       <c r="K13" s="11" t="n"/>
       <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+      <c r="M13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="15.5" customHeight="1">
       <c r="B14" s="10" t="n">
         <v>9</v>
       </c>
@@ -2110,16 +2170,14 @@
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
+      <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="J14" s="11" t="n"/>
       <c r="K14" s="11" t="n"/>
       <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+      <c r="M14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="15.5" customHeight="1">
       <c r="B15" s="10" t="n">
         <v>10</v>
       </c>
@@ -2128,16 +2186,14 @@
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="11" t="n"/>
       <c r="K15" s="11" t="n"/>
       <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+      <c r="M15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="15.5" customHeight="1">
       <c r="B16" s="10" t="n">
         <v>11</v>
       </c>
@@ -2146,16 +2202,14 @@
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="J16" s="11" t="n"/>
       <c r="K16" s="11" t="n"/>
       <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+      <c r="M16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="15.5" customHeight="1">
       <c r="B17" s="10" t="n">
         <v>12</v>
       </c>
@@ -2164,16 +2218,14 @@
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="11" t="n"/>
       <c r="K17" s="11" t="n"/>
       <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+      <c r="M17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="15.5" customHeight="1">
       <c r="B18" s="10" t="n">
         <v>13</v>
       </c>
@@ -2182,16 +2234,14 @@
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+      <c r="M18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="15.5" customHeight="1">
       <c r="B19" s="10" t="n">
         <v>14</v>
       </c>
@@ -2200,16 +2250,14 @@
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
+      <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
+      <c r="J19" s="11" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+      <c r="M19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="15.5" customHeight="1">
       <c r="B20" s="10" t="n">
         <v>15</v>
       </c>
@@ -2218,16 +2266,14 @@
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
+      <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
+      <c r="J20" s="11" t="n"/>
       <c r="K20" s="11" t="n"/>
       <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+      <c r="M20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="15.5" customHeight="1">
       <c r="B21" s="10" t="n">
         <v>16</v>
       </c>
@@ -2236,16 +2282,14 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="11" t="n"/>
       <c r="K21" s="11" t="n"/>
       <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+      <c r="M21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="15.5" customHeight="1">
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -2257,19 +2301,17 @@
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>참가비 내역 (자동 계산)</t>
         </is>
       </c>
+      <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+    </row>
+    <row r="23" ht="15.5" customHeight="1">
       <c r="B23" s="10" t="n">
         <v>1</v>
       </c>
@@ -2286,38 +2328,36 @@
       <c r="E23" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="K23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="O23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+    </row>
+    <row r="24" ht="15.5" customHeight="1">
       <c r="B24" s="10" t="n">
         <v>2</v>
       </c>
@@ -2332,34 +2372,32 @@
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>개인전 참가비</t>
         </is>
       </c>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="16" t="n">
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="16" t="n">
         <v>35000</v>
       </c>
-      <c r="M24" s="17">
-        <f>COUNTA(C6:C21)+COUNTA(J6:J21)+COUNTA(C23:C34)</f>
+      <c r="L24" s="17">
+        <f>COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34)</f>
         <v/>
       </c>
-      <c r="N24" s="18">
-        <f>L24*M24</f>
+      <c r="M24" s="18">
+        <f>K24*L24</f>
         <v/>
       </c>
-      <c r="O24" s="15" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+    </row>
+    <row r="25" ht="15.5" customHeight="1">
       <c r="B25" s="10" t="n">
         <v>3</v>
       </c>
@@ -2367,29 +2405,27 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>챔프전 참가비</t>
         </is>
       </c>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="16" t="n">
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="M25" s="17">
-        <f>COUNTIF(H6:H21,"O")</f>
+      <c r="L25" s="17">
+        <f>COUNTIF(G6:G21,"O")</f>
         <v/>
       </c>
-      <c r="N25" s="18">
-        <f>L25*M25</f>
+      <c r="M25" s="18">
+        <f>K25*L25</f>
         <v/>
       </c>
-      <c r="O25" s="15" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+    </row>
+    <row r="26" ht="15.5" customHeight="1">
       <c r="B26" s="10" t="n">
         <v>4</v>
       </c>
@@ -2397,29 +2433,27 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>사이드 참가비</t>
         </is>
       </c>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="16" t="n">
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="M26" s="17">
-        <f>COUNTIF(G6:G21,"O")+COUNTIF(N6:N21,"O")+COUNTIF(G23:G34,"O")</f>
+      <c r="L26" s="17">
+        <f>COUNTIF(F6:F21,"O")+COUNTIF(L6:L21,"O")+COUNTIF(F23:F34,"O")</f>
         <v/>
       </c>
-      <c r="N26" s="18">
-        <f>L26*M26</f>
+      <c r="M26" s="18">
+        <f>K26*L26</f>
         <v/>
       </c>
-      <c r="O26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+    </row>
+    <row r="27" ht="15.5" customHeight="1">
       <c r="B27" s="10" t="n">
         <v>5</v>
       </c>
@@ -2427,28 +2461,26 @@
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>클럽 참가비</t>
         </is>
       </c>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="16" t="n">
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="16" t="n">
         <v>110000</v>
       </c>
-      <c r="M27" s="17" t="n">
+      <c r="L27" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="18">
-        <f>L27*M27</f>
+      <c r="M27" s="18">
+        <f>K27*L27</f>
         <v/>
       </c>
-      <c r="O27" s="15" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+    </row>
+    <row r="28" ht="15.5" customHeight="1">
       <c r="B28" s="10" t="n">
         <v>6</v>
       </c>
@@ -2456,28 +2488,26 @@
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>클럽 찬조금</t>
         </is>
       </c>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="16" t="n">
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="16" t="n">
         <v>50000</v>
       </c>
-      <c r="M28" s="17" t="n">
+      <c r="L28" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="18">
-        <f>L28*M28</f>
+      <c r="M28" s="18">
+        <f>K28*L28</f>
         <v/>
       </c>
-      <c r="O28" s="15" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+    </row>
+    <row r="29" ht="15.5" customHeight="1">
       <c r="B29" s="10" t="n">
         <v>7</v>
       </c>
@@ -2485,23 +2515,21 @@
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>개인 찬조</t>
         </is>
       </c>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="16" t="n">
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="O29" s="15" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+    </row>
+    <row r="30" ht="15.5" customHeight="1">
       <c r="B30" s="10" t="n">
         <v>8</v>
       </c>
@@ -2509,24 +2537,22 @@
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
+      <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="20">
-        <f>SUM(N24:N29)</f>
+      <c r="M30" s="20">
+        <f>SUM(M24:M29)</f>
         <v/>
       </c>
-      <c r="O30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+    </row>
+    <row r="31" ht="15.5" customHeight="1">
       <c r="B31" s="10" t="n">
         <v>9</v>
       </c>
@@ -2534,16 +2560,15 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당(여성 15 등), 시니어핸디는 별도 칸(합산). 프로 감점 등은 핸디에 음수로 적고 비고에 표시.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당 합계(여성 15, 시니어 1~5, 프로 감점 등 합산)로 적고 내역은 비고에.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.5" customHeight="1">
       <c r="B32" s="10" t="n">
         <v>10</v>
       </c>
@@ -2551,11 +2576,10 @@
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="15.5" customHeight="1">
       <c r="B33" s="10" t="n">
         <v>11</v>
       </c>
@@ -2563,11 +2587,10 @@
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="15.5" customHeight="1">
       <c r="B34" s="10" t="n">
         <v>12</v>
       </c>
@@ -2575,13 +2598,12 @@
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="15.5" customHeight="1">
       <c r="B35" s="22">
-        <f>"총 인원 "&amp;(COUNTA(C6:C21)+COUNTA(J6:J21)+COUNTA(C23:C34))&amp;"명 (1조 "&amp;COUNTA(C6:C21)&amp;"명, 2조 "&amp;COUNTA(J6:J21)&amp;"명, 3조 "&amp;COUNTA(C23:C34)&amp;"명, 챔프전 "&amp;M25&amp;"명, 사이드 "&amp;M26&amp;"명)"</f>
+        <f>"총 인원 "&amp;(COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34))&amp;"명 (1조 "&amp;COUNTA(C6:C21)&amp;"명, 2조 "&amp;COUNTA(I6:I21)&amp;"명, 3조 "&amp;COUNTA(C23:C34)&amp;"명, 챔프전 "&amp;L25&amp;"명, 사이드 "&amp;L26&amp;"명)"</f>
         <v/>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -2595,66 +2617,151 @@
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
+    </row>
+    <row r="36" ht="15.5" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
           <t>3인조</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>선수1</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>선수2</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>선수3</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="15.5" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>지역 대표 3명</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>홍길동</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>남</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>3인조: 지역 대표 3명 (개인전 합계로 지역 순위 포인트)   스카치: 남 1 + 여 1   베이커: 3명</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="15" t="n"/>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>박철수</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>남</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>최민수</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>남</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15.5" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>스카치</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>선수1</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>선수2</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="15.5" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>남1 + 여1
+2게임</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
@@ -2670,373 +2777,421 @@
           <t>남</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>팀 순서대로 번호가 붙습니다 (지역명1, 지역명2 …). 핸디(베이커 여성 +3/+5 등)는 대회에서 적용합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="15" t="n"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="15.5" customHeight="1">
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
+          <t>박철수</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>이순자</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="15.5" customHeight="1">
+      <c r="A41" s="24" t="n"/>
+      <c r="B41" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>최민수</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>정미라</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="15.5" customHeight="1">
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="15.5" customHeight="1">
+      <c r="A43" s="25" t="n"/>
+      <c r="B43" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="15.5" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>베이커</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>선수1</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>선수2</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>선수3</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="15.5" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>3인
+2게임</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>박철수</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>최민수</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="15.5" customHeight="1">
+      <c r="A46" s="24" t="n"/>
+      <c r="B46" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
           <t>김영희</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>여</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="15" t="n"/>
-      <c r="B41" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>박철수</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="15" t="n"/>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>이순자</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>여</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="15" t="n"/>
-      <c r="B43" s="10" t="n">
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>정미라</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="15.5" customHeight="1">
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>최민수</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="15" t="n"/>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>정미라</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="15" t="n"/>
-      <c r="B45" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="15" t="n"/>
-      <c r="B46" s="15" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="15" t="n"/>
-      <c r="B47" s="10" t="n">
-        <v>5</v>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="15" t="n"/>
-      <c r="B48" s="15" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="15.5" customHeight="1">
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>베이커</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="15.5" customHeight="1">
+      <c r="A49" s="25" t="n"/>
       <c r="B49" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="15" t="n"/>
-      <c r="B50" s="15" t="n"/>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>박철수</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="15" t="n"/>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>최민수</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="15" t="n"/>
-      <c r="B52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>김영희</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="15" t="n"/>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>이순자</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="15" t="n"/>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>정미라</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="15" t="n"/>
-      <c r="B55" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="15" t="n"/>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="11" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="15" t="n"/>
-      <c r="B57" s="15" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="11" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="15" t="n"/>
-      <c r="B58" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="11" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="15" t="n"/>
-      <c r="B59" s="15" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="11" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="15" t="n"/>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="11" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="15" t="n"/>
-      <c r="B61" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="11" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="15" t="n"/>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="11" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="15" t="n"/>
-      <c r="B63" s="15" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="11" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="15.5" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
-      <c r="C64" s="20">
-        <f>N30</f>
+      <c r="C50" s="20">
+        <f>M30</f>
         <v/>
       </c>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="24" t="inlineStr">
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>입금계좌 : (대회 공지의 계좌)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="25" t="inlineStr">
+    <row r="51" ht="15.5" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>위와 같이 제46회 네이버 볼링 동호회 서울 전국대회 참가를 신청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1"/>
-    <row r="68" ht="15" customHeight="1"/>
-    <row r="69" ht="15" customHeight="1"/>
+    <row r="52" ht="15.5" customHeight="1"/>
+    <row r="53" ht="15.5" customHeight="1"/>
+    <row r="54" ht="15.5" customHeight="1"/>
+    <row r="55" ht="15.5" customHeight="1"/>
+    <row r="56" ht="15.5" customHeight="1"/>
+    <row r="57" ht="15.5" customHeight="1"/>
+    <row r="58" ht="15.5" customHeight="1"/>
+    <row r="59" ht="15.5" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="50">
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="A65:O65"/>
-    <mergeCell ref="B35:O35"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="F39:O48"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="A49:A63"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A39:A48"/>
-    <mergeCell ref="J24:K24"/>
+  <mergeCells count="58">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="I25:J25"/>
     <mergeCell ref="A4:A34"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="F64:O64"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E40:F40"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="J31:O33"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="I31:M34"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="B35:M35"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="A37"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="F36:O38"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="F49:O63"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation sqref="D6:D21 D23:D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="D6:D21 D23:D34 J6:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F21 F23:F34 G6:G21 L6:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D37 G37 I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:G21 G23:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N6:N21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H6:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D36:D38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D39:D43 G39:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D39:D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"남,여"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D49:D63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D45:D49 G45:G49 I45:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/signup-template.xlsx
+++ b/docs/signup-template.xlsx
@@ -11,8 +11,8 @@
     <sheet name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'참가신청서'!$A$1:$M$51</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$M$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'참가신청서'!$A$1:$M$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$M$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,12 @@
       <color rgb="00595959"/>
       <sz val="7.5"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -113,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -135,44 +141,11 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -236,14 +209,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -615,10 +589,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6.5" customWidth="1" min="1" max="1"/>
     <col width="4.5" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="4.5" customWidth="1" min="4" max="4"/>
@@ -633,21 +607,21 @@
     <col width="9.5" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>제46회 네이버 볼링 동호회 서울 전국대회 참가 신청서</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.5" customHeight="1">
+    <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란 칸만 입력 · 대표/팀 명단에는 개인전 명단과 똑같은 이름 · 챔프전은 1조만 · 사이드·챔프전 참가는 O 표시 · 수량·금액은 자동 계산</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.5" customHeight="1">
+          <t>노란 칸만 입력 · 3인조/팀 명단에는 개인전 명단과 똑같은 이름 · 챔프전은 1조만 · 사이드·챔프전 참가는 O 표시 · 수량·금액은 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>클럽명</t>
@@ -671,7 +645,7 @@
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="5" t="n"/>
     </row>
-    <row r="4" ht="15.5" customHeight="1">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>개인전</t>
@@ -702,7 +676,7 @@
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
     </row>
-    <row r="5" ht="15.5" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -760,7 +734,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="B6" s="10" t="n">
         <v>1</v>
       </c>
@@ -776,7 +750,7 @@
       <c r="L6" s="11" t="n"/>
       <c r="M6" s="4" t="n"/>
     </row>
-    <row r="7" ht="15.5" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="B7" s="10" t="n">
         <v>2</v>
       </c>
@@ -792,7 +766,7 @@
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="4" t="n"/>
     </row>
-    <row r="8" ht="15.5" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="B8" s="10" t="n">
         <v>3</v>
       </c>
@@ -808,7 +782,7 @@
       <c r="L8" s="11" t="n"/>
       <c r="M8" s="4" t="n"/>
     </row>
-    <row r="9" ht="15.5" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="B9" s="10" t="n">
         <v>4</v>
       </c>
@@ -824,7 +798,7 @@
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="4" t="n"/>
     </row>
-    <row r="10" ht="15.5" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="B10" s="10" t="n">
         <v>5</v>
       </c>
@@ -840,7 +814,7 @@
       <c r="L10" s="11" t="n"/>
       <c r="M10" s="4" t="n"/>
     </row>
-    <row r="11" ht="15.5" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="10" t="n">
         <v>6</v>
       </c>
@@ -856,7 +830,7 @@
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="4" t="n"/>
     </row>
-    <row r="12" ht="15.5" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="B12" s="10" t="n">
         <v>7</v>
       </c>
@@ -872,7 +846,7 @@
       <c r="L12" s="11" t="n"/>
       <c r="M12" s="4" t="n"/>
     </row>
-    <row r="13" ht="15.5" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="B13" s="10" t="n">
         <v>8</v>
       </c>
@@ -888,7 +862,7 @@
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="4" t="n"/>
     </row>
-    <row r="14" ht="15.5" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="B14" s="10" t="n">
         <v>9</v>
       </c>
@@ -904,7 +878,7 @@
       <c r="L14" s="11" t="n"/>
       <c r="M14" s="4" t="n"/>
     </row>
-    <row r="15" ht="15.5" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="10" t="n">
         <v>10</v>
       </c>
@@ -920,7 +894,7 @@
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="4" t="n"/>
     </row>
-    <row r="16" ht="15.5" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="B16" s="10" t="n">
         <v>11</v>
       </c>
@@ -936,7 +910,7 @@
       <c r="L16" s="11" t="n"/>
       <c r="M16" s="4" t="n"/>
     </row>
-    <row r="17" ht="15.5" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="B17" s="10" t="n">
         <v>12</v>
       </c>
@@ -952,7 +926,7 @@
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="4" t="n"/>
     </row>
-    <row r="18" ht="15.5" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="B18" s="10" t="n">
         <v>13</v>
       </c>
@@ -968,7 +942,7 @@
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="4" t="n"/>
     </row>
-    <row r="19" ht="15.5" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="B19" s="10" t="n">
         <v>14</v>
       </c>
@@ -984,7 +958,7 @@
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="4" t="n"/>
     </row>
-    <row r="20" ht="15.5" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="B20" s="10" t="n">
         <v>15</v>
       </c>
@@ -1000,7 +974,7 @@
       <c r="L20" s="11" t="n"/>
       <c r="M20" s="4" t="n"/>
     </row>
-    <row r="21" ht="15.5" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="B21" s="10" t="n">
         <v>16</v>
       </c>
@@ -1016,147 +990,95 @@
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="4" t="n"/>
     </row>
-    <row r="22" ht="15.5" customHeight="1">
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>3조</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>참가비 내역 (자동 계산)</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="15.5" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
+      <c r="B22" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
       <c r="B23" s="10" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="11" t="n"/>
-      <c r="G23" s="13" t="n"/>
+      <c r="G23" s="11" t="n"/>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>금액</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15.5" customHeight="1">
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
       <c r="B24" s="10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="11" t="n"/>
-      <c r="G24" s="13" t="n"/>
+      <c r="G24" s="11" t="n"/>
       <c r="H24" s="4" t="n"/>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>개인전 참가비</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="16" t="n">
-        <v>35000</v>
-      </c>
-      <c r="L24" s="17">
-        <f>COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34)</f>
-        <v/>
-      </c>
-      <c r="M24" s="18">
-        <f>K24*L24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15.5" customHeight="1">
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
       <c r="B25" s="10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="13" t="n"/>
+      <c r="G25" s="11" t="n"/>
       <c r="H25" s="4" t="n"/>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>챔프전 참가비</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="n"/>
-      <c r="K25" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L25" s="17">
-        <f>COUNTIF(G6:G21,"O")</f>
-        <v/>
-      </c>
-      <c r="M25" s="18">
-        <f>K25*L25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15.5" customHeight="1">
-      <c r="B26" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>사이드 참가비</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L26" s="17">
-        <f>COUNTIF(F6:F21,"O")+COUNTIF(L6:L21,"O")+COUNTIF(F23:F34,"O")</f>
-        <v/>
-      </c>
-      <c r="M26" s="18">
-        <f>K26*L26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15.5" customHeight="1">
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>3조</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>참가비 내역 (자동 계산)</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
       <c r="B27" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="11" t="n"/>
@@ -1164,26 +1086,31 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
       <c r="H27" s="4" t="n"/>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>클럽 참가비</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="16" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="18">
-        <f>K27*L27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15.5" customHeight="1">
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
       <c r="B28" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="11" t="n"/>
@@ -1193,24 +1120,25 @@
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>클럽 찬조금</t>
+          <t>개인전 참가비</t>
         </is>
       </c>
       <c r="J28" s="15" t="n"/>
       <c r="K28" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>1</v>
+        <v>35000</v>
+      </c>
+      <c r="L28" s="17">
+        <f>COUNTA(C6:C25)+COUNTA(I6:I25)+COUNTA(C27:C46)</f>
+        <v/>
       </c>
       <c r="M28" s="18">
         <f>K28*L28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15.5" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="B29" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="11" t="n"/>
@@ -1220,19 +1148,25 @@
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>개인 찬조</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.5" customHeight="1">
+          <t>챔프전 참가비</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L29" s="17">
+        <f>COUNTIF(G6:G25,"O")</f>
+        <v/>
+      </c>
+      <c r="M29" s="18">
+        <f>K29*L29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
       <c r="B30" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="11" t="n"/>
@@ -1240,22 +1174,27 @@
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="13" t="n"/>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>총금액</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="20">
-        <f>SUM(M24:M29)</f>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>사이드 참가비</t>
+        </is>
+      </c>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L30" s="17">
+        <f>COUNTIF(F6:F25,"O")+COUNTIF(L6:L25,"O")+COUNTIF(F27:F46,"O")</f>
         <v/>
       </c>
-    </row>
-    <row r="31" ht="15.5" customHeight="1">
+      <c r="M30" s="18">
+        <f>K30*L30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
       <c r="B31" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="11" t="n"/>
@@ -1263,15 +1202,26 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="13" t="n"/>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당 합계(여성 15, 시니어 1~5, 프로 감점 등 합산)로 적고 내역은 비고에.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.5" customHeight="1">
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>클럽 참가비</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="16" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18">
+        <f>K31*L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
       <c r="B32" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="11" t="n"/>
@@ -1279,10 +1229,26 @@
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="13" t="n"/>
       <c r="H32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="15.5" customHeight="1">
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>클럽 찬조금</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="18">
+        <f>K32*L32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
       <c r="B33" s="10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="11" t="n"/>
@@ -1290,10 +1256,21 @@
       <c r="F33" s="11" t="n"/>
       <c r="G33" s="13" t="n"/>
       <c r="H33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15.5" customHeight="1">
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>개인 찬조</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
       <c r="B34" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="11" t="n"/>
@@ -1301,478 +1278,637 @@
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="13" t="n"/>
       <c r="H34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.5" customHeight="1">
-      <c r="B35" s="22">
-        <f>"총 인원 "&amp;(COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34))&amp;"명 (1조 "&amp;COUNTA(C6:C21)&amp;"명, 2조 "&amp;COUNTA(I6:I21)&amp;"명, 3조 "&amp;COUNTA(C23:C34)&amp;"명, 챔프전 "&amp;L25&amp;"명, 사이드 "&amp;L26&amp;"명)"</f>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>총금액</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="20">
+        <f>SUM(M28:M33)</f>
         <v/>
       </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="15.5" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>3인조</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>선수1</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>선수2</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>선수3</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="15.5" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>지역 대표 3명</t>
-        </is>
-      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="B35" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당 합계(여성 15, 시니어 1~5, 프로 감점 등 합산)로 적고 내역은 비고에.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="B36" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="14" customHeight="1">
       <c r="B37" s="10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="11" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="13" t="n"/>
       <c r="H37" s="4" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="15.5" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>스카치</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>선수1</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>선수2</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="B38" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>3인조</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>지역 대표 3명 (개인전 합산 → 지역 포인트)</t>
+        </is>
+      </c>
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="5" t="n"/>
     </row>
-    <row r="39" ht="15.5" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>남1 + 여1
-2게임</t>
-        </is>
-      </c>
+    <row r="39" ht="14" customHeight="1">
       <c r="B39" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="11" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="13" t="n"/>
       <c r="H39" s="4" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="15.5" customHeight="1">
-      <c r="A40" s="24" t="n"/>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
       <c r="B40" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="11" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="13" t="n"/>
       <c r="H40" s="4" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="15.5" customHeight="1">
-      <c r="A41" s="24" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="14" customHeight="1">
       <c r="B41" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="11" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="13" t="n"/>
       <c r="H41" s="4" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="15.5" customHeight="1">
-      <c r="A42" s="24" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="14" customHeight="1">
       <c r="B42" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="11" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="4" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="15.5" customHeight="1">
-      <c r="A43" s="25" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="14" customHeight="1">
       <c r="B43" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="11" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="15.5" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>베이커</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>선수1</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>선수2</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>선수3</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="15.5" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>3인
-2게임</t>
-        </is>
-      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="B44" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="14" customHeight="1">
       <c r="B45" s="10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="11" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="13" t="n"/>
       <c r="H45" s="4" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="15.5" customHeight="1">
-      <c r="A46" s="24" t="n"/>
+    </row>
+    <row r="46" ht="14" customHeight="1">
       <c r="B46" s="10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="11" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="13" t="n"/>
       <c r="H46" s="4" t="n"/>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="15.5" customHeight="1">
-      <c r="A47" s="24" t="n"/>
-      <c r="B47" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="4" t="n"/>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="B47" s="24">
+        <f>"총 인원 "&amp;(COUNTA(C6:C25)+COUNTA(I6:I25)+COUNTA(C27:C46))&amp;"명 (1조 "&amp;COUNTA(C6:C25)&amp;"명, 2조 "&amp;COUNTA(I6:I25)&amp;"명, 3조 "&amp;COUNTA(C27:C46)&amp;"명, 챔프전 "&amp;L29&amp;"명, 사이드 "&amp;L30&amp;"명)"</f>
+        <v/>
+      </c>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="4" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="n"/>
     </row>
-    <row r="48" ht="15.5" customHeight="1">
-      <c r="A48" s="24" t="n"/>
-      <c r="B48" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="4" t="n"/>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>스카치 더블 (남1 + 여1 · 2게임)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="4" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>베이커 (3인 · 2게임)</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="n"/>
     </row>
-    <row r="49" ht="15.5" customHeight="1">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="10" t="n">
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="11" t="n"/>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="15" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="11" t="n"/>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="15" t="n"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="11" t="n"/>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="15" t="n"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="15" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="11" t="n"/>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="15" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="15" t="n"/>
+      <c r="B54" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="11" t="n"/>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="11" t="n"/>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="15" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="15" t="n"/>
+      <c r="B56" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="11" t="n"/>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="15" t="n"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="15" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="11" t="n"/>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="15" t="n"/>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="11" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="15.5" customHeight="1">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="11" t="n"/>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="15" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="15" t="n"/>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="11" t="n"/>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="15" t="n"/>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>팀 핸디는 팀원 핸디 칸의 합계로 적용됩니다. 베이커는 여성 1명 +3, 2명 이상 +5 (한 명 칸에 적어도 됨). 비워 두면 대회에서 규정대로 적용.</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="11" t="n"/>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="15" t="n"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="15" t="n"/>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="11" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="15" t="n"/>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="15" t="n"/>
+      <c r="H62" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="11" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="15" t="n"/>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="15" t="n"/>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="15" t="n"/>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="15" t="n"/>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="11" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="15" t="n"/>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
-      <c r="C50" s="20">
-        <f>M30</f>
+      <c r="C65" s="20">
+        <f>M34</f>
         <v/>
       </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>입금계좌 : (대회 공지의 계좌)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.5" customHeight="1">
-      <c r="A51" s="27" t="inlineStr">
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>위와 같이 제46회 네이버 볼링 동호회 서울 전국대회 참가를 신청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15.5" customHeight="1"/>
-    <row r="53" ht="15.5" customHeight="1"/>
-    <row r="54" ht="15.5" customHeight="1"/>
-    <row r="55" ht="15.5" customHeight="1"/>
-    <row r="56" ht="15.5" customHeight="1"/>
-    <row r="57" ht="15.5" customHeight="1"/>
-    <row r="58" ht="15.5" customHeight="1"/>
-    <row r="59" ht="15.5" customHeight="1"/>
+    <row r="67" ht="14" customHeight="1"/>
+    <row r="68" ht="14" customHeight="1"/>
+    <row r="69" ht="14" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="58">
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="E42:F42"/>
+  <mergeCells count="72">
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="F57:G57"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="E65:M65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="I26:M26"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:A34"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I22:M22"/>
-    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="J38:M38"/>
     <mergeCell ref="I28:J28"/>
-    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="B60:G64"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="I31:M34"/>
+    <mergeCell ref="I35:M36"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="L64:M64"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L63:M63"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="B35:M35"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="E50:M50"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="A37"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="F52:G52"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="L60:M60"/>
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A4:A46"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L49:M49"/>
     <mergeCell ref="C4:H4"/>
-    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="L61:M61"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="F53:G53"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="D6:D21 D23:D34 J6:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D25 D27:D46 J6:J25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F21 F23:F34 G6:G21 L6:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F25 F27:F46 G6:G25 L6:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
     </dataValidation>
-    <dataValidation sqref="D37 G37 I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J40:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D39:D43 G39:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D50:D59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D45:D49 G45:G49 I45:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J50:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1788,10 +1924,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6.5" customWidth="1" min="1" max="1"/>
     <col width="4.5" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="4.5" customWidth="1" min="4" max="4"/>
@@ -1806,21 +1942,21 @@
     <col width="9.5" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>제46회 네이버 볼링 동호회 서울 전국대회 참가 신청서</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.5" customHeight="1">
+    <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란 칸만 입력 · 대표/팀 명단에는 개인전 명단과 똑같은 이름 · 챔프전은 1조만 · 사이드·챔프전 참가는 O 표시 · 수량·금액은 자동 계산</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.5" customHeight="1">
+          <t>노란 칸만 입력 · 3인조/팀 명단에는 개인전 명단과 똑같은 이름 · 챔프전은 1조만 · 사이드·챔프전 참가는 O 표시 · 수량·금액은 자동 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>클럽명</t>
@@ -1856,7 +1992,7 @@
       </c>
       <c r="M3" s="5" t="n"/>
     </row>
-    <row r="4" ht="15.5" customHeight="1">
+    <row r="4" ht="14" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>개인전</t>
@@ -1887,7 +2023,7 @@
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
     </row>
-    <row r="5" ht="15.5" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -1945,7 +2081,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="B6" s="10" t="n">
         <v>1</v>
       </c>
@@ -1995,7 +2131,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.5" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="B7" s="10" t="n">
         <v>2</v>
       </c>
@@ -2043,7 +2179,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="B8" s="10" t="n">
         <v>3</v>
       </c>
@@ -2081,7 +2217,7 @@
       <c r="L8" s="11" t="n"/>
       <c r="M8" s="4" t="n"/>
     </row>
-    <row r="9" ht="15.5" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="B9" s="10" t="n">
         <v>4</v>
       </c>
@@ -2097,7 +2233,7 @@
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="4" t="n"/>
     </row>
-    <row r="10" ht="15.5" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="B10" s="10" t="n">
         <v>5</v>
       </c>
@@ -2113,7 +2249,7 @@
       <c r="L10" s="11" t="n"/>
       <c r="M10" s="4" t="n"/>
     </row>
-    <row r="11" ht="15.5" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="10" t="n">
         <v>6</v>
       </c>
@@ -2129,7 +2265,7 @@
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="4" t="n"/>
     </row>
-    <row r="12" ht="15.5" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="B12" s="10" t="n">
         <v>7</v>
       </c>
@@ -2145,7 +2281,7 @@
       <c r="L12" s="11" t="n"/>
       <c r="M12" s="4" t="n"/>
     </row>
-    <row r="13" ht="15.5" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="B13" s="10" t="n">
         <v>8</v>
       </c>
@@ -2161,7 +2297,7 @@
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="4" t="n"/>
     </row>
-    <row r="14" ht="15.5" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="B14" s="10" t="n">
         <v>9</v>
       </c>
@@ -2177,7 +2313,7 @@
       <c r="L14" s="11" t="n"/>
       <c r="M14" s="4" t="n"/>
     </row>
-    <row r="15" ht="15.5" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="10" t="n">
         <v>10</v>
       </c>
@@ -2193,7 +2329,7 @@
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="4" t="n"/>
     </row>
-    <row r="16" ht="15.5" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="B16" s="10" t="n">
         <v>11</v>
       </c>
@@ -2209,7 +2345,7 @@
       <c r="L16" s="11" t="n"/>
       <c r="M16" s="4" t="n"/>
     </row>
-    <row r="17" ht="15.5" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="B17" s="10" t="n">
         <v>12</v>
       </c>
@@ -2225,7 +2361,7 @@
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="4" t="n"/>
     </row>
-    <row r="18" ht="15.5" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="B18" s="10" t="n">
         <v>13</v>
       </c>
@@ -2241,7 +2377,7 @@
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="4" t="n"/>
     </row>
-    <row r="19" ht="15.5" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="B19" s="10" t="n">
         <v>14</v>
       </c>
@@ -2257,7 +2393,7 @@
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="4" t="n"/>
     </row>
-    <row r="20" ht="15.5" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="B20" s="10" t="n">
         <v>15</v>
       </c>
@@ -2273,7 +2409,7 @@
       <c r="L20" s="11" t="n"/>
       <c r="M20" s="4" t="n"/>
     </row>
-    <row r="21" ht="15.5" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="B21" s="10" t="n">
         <v>16</v>
       </c>
@@ -2289,227 +2425,181 @@
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="4" t="n"/>
     </row>
-    <row r="22" ht="15.5" customHeight="1">
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>3조</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>참가비 내역 (자동 계산)</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="15.5" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
+      <c r="B22" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
       <c r="B23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>정미라</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>금액</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15.5" customHeight="1">
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
       <c r="B24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>강동원</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
       <c r="H24" s="4" t="n"/>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>개인전 참가비</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="16" t="n">
-        <v>35000</v>
-      </c>
-      <c r="L24" s="17">
-        <f>COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34)</f>
-        <v/>
-      </c>
-      <c r="M24" s="18">
-        <f>K24*L24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15.5" customHeight="1">
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
       <c r="B25" s="10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="13" t="n"/>
+      <c r="G25" s="11" t="n"/>
       <c r="H25" s="4" t="n"/>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>챔프전 참가비</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="n"/>
-      <c r="K25" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L25" s="17">
-        <f>COUNTIF(G6:G21,"O")</f>
-        <v/>
-      </c>
-      <c r="M25" s="18">
-        <f>K25*L25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15.5" customHeight="1">
-      <c r="B26" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>사이드 참가비</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L26" s="17">
-        <f>COUNTIF(F6:F21,"O")+COUNTIF(L6:L21,"O")+COUNTIF(F23:F34,"O")</f>
-        <v/>
-      </c>
-      <c r="M26" s="18">
-        <f>K26*L26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15.5" customHeight="1">
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>3조</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>참가비 내역 (자동 계산)</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
       <c r="B27" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>정미라</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G27" s="13" t="n"/>
       <c r="H27" s="4" t="n"/>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>클럽 참가비</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="16" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="18">
-        <f>K27*L27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15.5" customHeight="1">
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
       <c r="B28" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="11" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>강동원</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
       <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G28" s="13" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>클럽 찬조금</t>
+          <t>개인전 참가비</t>
         </is>
       </c>
       <c r="J28" s="15" t="n"/>
       <c r="K28" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>1</v>
+        <v>35000</v>
+      </c>
+      <c r="L28" s="17">
+        <f>COUNTA(C6:C25)+COUNTA(I6:I25)+COUNTA(C27:C46)</f>
+        <v/>
       </c>
       <c r="M28" s="18">
         <f>K28*L28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15.5" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="B29" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="11" t="n"/>
@@ -2519,19 +2609,25 @@
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>개인 찬조</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="16" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="30" ht="15.5" customHeight="1">
+          <t>챔프전 참가비</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L29" s="17">
+        <f>COUNTIF(G6:G25,"O")</f>
+        <v/>
+      </c>
+      <c r="M29" s="18">
+        <f>K29*L29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
       <c r="B30" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="11" t="n"/>
@@ -2539,22 +2635,27 @@
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="13" t="n"/>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>총금액</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="20">
-        <f>SUM(M24:M29)</f>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>사이드 참가비</t>
+        </is>
+      </c>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L30" s="17">
+        <f>COUNTIF(F6:F25,"O")+COUNTIF(L6:L25,"O")+COUNTIF(F27:F46,"O")</f>
         <v/>
       </c>
-    </row>
-    <row r="31" ht="15.5" customHeight="1">
+      <c r="M30" s="18">
+        <f>K30*L30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
       <c r="B31" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="11" t="n"/>
@@ -2562,15 +2663,26 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="13" t="n"/>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당 합계(여성 15, 시니어 1~5, 프로 감점 등 합산)로 적고 내역은 비고에.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.5" customHeight="1">
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>클럽 참가비</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="16" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18">
+        <f>K31*L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
       <c r="B32" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="11" t="n"/>
@@ -2578,10 +2690,26 @@
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="13" t="n"/>
       <c r="H32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="15.5" customHeight="1">
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>클럽 찬조금</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="18">
+        <f>K32*L32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
       <c r="B33" s="10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="11" t="n"/>
@@ -2589,10 +2717,21 @@
       <c r="F33" s="11" t="n"/>
       <c r="G33" s="13" t="n"/>
       <c r="H33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15.5" customHeight="1">
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>개인 찬조</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="16" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
       <c r="B34" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="11" t="n"/>
@@ -2600,598 +2739,789 @@
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="13" t="n"/>
       <c r="H34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.5" customHeight="1">
-      <c r="B35" s="22">
-        <f>"총 인원 "&amp;(COUNTA(C6:C21)+COUNTA(I6:I21)+COUNTA(C23:C34))&amp;"명 (1조 "&amp;COUNTA(C6:C21)&amp;"명, 2조 "&amp;COUNTA(I6:I21)&amp;"명, 3조 "&amp;COUNTA(C23:C34)&amp;"명, 챔프전 "&amp;L25&amp;"명, 사이드 "&amp;L26&amp;"명)"</f>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>총금액</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="20">
+        <f>SUM(M28:M33)</f>
         <v/>
       </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="15.5" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="B35" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>단가는 대회 공지 기준으로 수정. 핸디는 게임당 합계(여성 15, 시니어 1~5, 프로 감점 등 합산)로 적고 내역은 비고에.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="B36" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="B37" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="B38" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>3인조</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>선수1</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>선수2</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>선수3</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="15.5" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>지역 대표 3명</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>박철수</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>최민수</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="15.5" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>스카치</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>선수1</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>선수2</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>지역 대표 3명 (개인전 합산 → 지역 포인트)</t>
+        </is>
+      </c>
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="5" t="n"/>
     </row>
-    <row r="39" ht="15.5" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>남1 + 여1
-2게임</t>
-        </is>
-      </c>
+    <row r="39" ht="14" customHeight="1">
       <c r="B39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="B40" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>홍길동</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>남</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>김영희</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="15.5" customHeight="1">
-      <c r="A40" s="24" t="n"/>
-      <c r="B40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="B41" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>박철수</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>남</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>이순자</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="15.5" customHeight="1">
-      <c r="A41" s="24" t="n"/>
-      <c r="B41" s="10" t="n">
+      <c r="K41" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>최민수</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>정미라</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="15.5" customHeight="1">
-      <c r="A42" s="24" t="n"/>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>시니어</t>
+        </is>
+      </c>
+      <c r="M41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="14" customHeight="1">
       <c r="B42" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="11" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="4" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="15.5" customHeight="1">
-      <c r="A43" s="25" t="n"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>최민수</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>프로</t>
+        </is>
+      </c>
+      <c r="M42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="14" customHeight="1">
       <c r="B43" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="11" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="15.5" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>베이커</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>선수1</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>선수2</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>선수3</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="15.5" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>3인
-2게임</t>
-        </is>
-      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="B44" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="14" customHeight="1">
       <c r="B45" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>박철수</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>최민수</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="15.5" customHeight="1">
-      <c r="A46" s="24" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="14" customHeight="1">
       <c r="B46" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>김영희</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>이순자</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>정미라</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="15.5" customHeight="1">
-      <c r="A47" s="24" t="n"/>
-      <c r="B47" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="4" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="B47" s="24">
+        <f>"총 인원 "&amp;(COUNTA(C6:C25)+COUNTA(I6:I25)+COUNTA(C27:C46))&amp;"명 (1조 "&amp;COUNTA(C6:C25)&amp;"명, 2조 "&amp;COUNTA(I6:I25)&amp;"명, 3조 "&amp;COUNTA(C27:C46)&amp;"명, 챔프전 "&amp;L29&amp;"명, 사이드 "&amp;L30&amp;"명)"</f>
+        <v/>
+      </c>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="4" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="n"/>
     </row>
-    <row r="48" ht="15.5" customHeight="1">
-      <c r="A48" s="24" t="n"/>
-      <c r="B48" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="4" t="n"/>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>스카치 더블 (남1 + 여1 · 2게임)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="4" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>베이커 (3인 · 2게임)</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="n"/>
     </row>
-    <row r="49" ht="15.5" customHeight="1">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="10" t="n">
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>핸디</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="15" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>박철수</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="15" t="n"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>박철수</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>최민수</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="15" t="n"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="15" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>이순자</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>김영희</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="15" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="15" t="n"/>
+      <c r="B54" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>최민수</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>프로</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>이순자</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>정미라</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>정미라</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>여</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="11" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="15.5" customHeight="1">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>여성 3명 +5</t>
+        </is>
+      </c>
+      <c r="M55" s="15" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="15" t="n"/>
+      <c r="B56" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="11" t="n"/>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="15" t="n"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="15" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="11" t="n"/>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="15" t="n"/>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="11" t="n"/>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="15" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="15" t="n"/>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="11" t="n"/>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="15" t="n"/>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>팀 핸디는 팀원 핸디 칸의 합계로 적용됩니다. 베이커는 여성 1명 +3, 2명 이상 +5 (한 명 칸에 적어도 됨). 비워 두면 대회에서 규정대로 적용.</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="11" t="n"/>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="15" t="n"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="15" t="n"/>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="11" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="15" t="n"/>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="15" t="n"/>
+      <c r="H62" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="11" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="15" t="n"/>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="15" t="n"/>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="15" t="n"/>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="15" t="n"/>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="11" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="15" t="n"/>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
-      <c r="C50" s="20">
-        <f>M30</f>
+      <c r="C65" s="20">
+        <f>M34</f>
         <v/>
       </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>입금계좌 : (대회 공지의 계좌)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.5" customHeight="1">
-      <c r="A51" s="27" t="inlineStr">
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>위와 같이 제46회 네이버 볼링 동호회 서울 전국대회 참가를 신청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15.5" customHeight="1"/>
-    <row r="53" ht="15.5" customHeight="1"/>
-    <row r="54" ht="15.5" customHeight="1"/>
-    <row r="55" ht="15.5" customHeight="1"/>
-    <row r="56" ht="15.5" customHeight="1"/>
-    <row r="57" ht="15.5" customHeight="1"/>
-    <row r="58" ht="15.5" customHeight="1"/>
-    <row r="59" ht="15.5" customHeight="1"/>
+    <row r="67" ht="14" customHeight="1"/>
+    <row r="68" ht="14" customHeight="1"/>
+    <row r="69" ht="14" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="58">
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="E42:F42"/>
+  <mergeCells count="72">
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="F57:G57"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="E65:M65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="I26:M26"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:A34"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I22:M22"/>
-    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="J38:M38"/>
     <mergeCell ref="I28:J28"/>
-    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="B60:G64"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="I31:M34"/>
+    <mergeCell ref="I35:M36"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="L64:M64"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L63:M63"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="B35:M35"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="E50:M50"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="A37"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="F52:G52"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="L60:M60"/>
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A4:A46"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="L49:M49"/>
     <mergeCell ref="C4:H4"/>
-    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="L61:M61"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="F53:G53"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="D6:D21 D23:D34 J6:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D25 D27:D46 J6:J25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F21 F23:F34 G6:G21 L6:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F25 F27:F46 G6:G25 L6:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
     </dataValidation>
-    <dataValidation sqref="D37 G37 I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J40:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D39:D43 G39:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D50:D59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D45:D49 G45:G49 I45:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J50:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/signup-template.xlsx
+++ b/docs/signup-template.xlsx
@@ -11,8 +11,8 @@
     <sheet name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'참가신청서'!$A$1:$M$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$M$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'참가신청서'!$A$1:$M$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$M$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -1742,11 +1742,14 @@
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="15" t="n"/>
-      <c r="B60" s="21" t="inlineStr">
-        <is>
-          <t>팀 핸디는 팀원 핸디 칸의 합계로 적용됩니다. 베이커는 여성 1명 +3, 2명 이상 +5 (한 명 칸에 적어도 됨). 비워 두면 대회에서 규정대로 적용.</t>
-        </is>
-      </c>
+      <c r="B60" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="11" t="n"/>
@@ -1756,6 +1759,12 @@
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="15" t="n"/>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="15" t="n"/>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="11" t="n"/>
@@ -1765,6 +1774,14 @@
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="15" t="n"/>
+      <c r="B62" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="15" t="n"/>
       <c r="H62" s="10" t="n">
         <v>5</v>
       </c>
@@ -1776,6 +1793,12 @@
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="15" t="n"/>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="11" t="n"/>
@@ -1785,6 +1808,14 @@
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="15" t="n"/>
+      <c r="B64" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="11" t="n"/>
@@ -1793,106 +1824,330 @@
       <c r="M64" s="15" t="n"/>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="15" t="n"/>
+      <c r="H65" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="15" t="n"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="15" t="n"/>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="11" t="n"/>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="15" t="n"/>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="15" t="n"/>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="11" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="15" t="n"/>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="11" t="n"/>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="15" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="15" t="n"/>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="15" t="n"/>
+      <c r="B70" s="21" t="inlineStr">
+        <is>
+          <t>팀 핸디는 팀원 핸디 칸의 합계로 적용됩니다. 베이커는 여성 1명 +3, 2명 이상 +5 (한 명 칸에 적어도 됨). 비워 두면 대회에서 규정대로 적용.</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="4" t="n"/>
+      <c r="J70" s="11" t="n"/>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="15" t="n"/>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="15" t="n"/>
+      <c r="H71" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="15" t="n"/>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="15" t="n"/>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="11" t="n"/>
+      <c r="K72" s="11" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="15" t="n"/>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="15" t="n"/>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="11" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="15" t="n"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="15" t="n"/>
+      <c r="H74" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="11" t="n"/>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="15" t="n"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="15" t="n"/>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="15" t="n"/>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="11" t="n"/>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="15" t="n"/>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="15" t="n"/>
+      <c r="H77" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="15" t="n"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="15" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="4" t="n"/>
+      <c r="J78" s="11" t="n"/>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="15" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="15" t="n"/>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="11" t="n"/>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="15" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
-      <c r="C65" s="20">
+      <c r="C80" s="20">
         <f>M34</f>
         <v/>
       </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="25" t="inlineStr">
         <is>
           <t>입금계좌 : (대회 공지의 계좌)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="26" t="inlineStr">
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>위와 같이 제46회 네이버 볼링 동호회 서울 전국대회 참가를 신청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1"/>
-    <row r="68" ht="14" customHeight="1"/>
-    <row r="69" ht="14" customHeight="1"/>
+    <row r="82" ht="14" customHeight="1"/>
+    <row r="83" ht="14" customHeight="1"/>
+    <row r="84" ht="14" customHeight="1"/>
+    <row r="85" ht="14" customHeight="1"/>
+    <row r="86" ht="14" customHeight="1"/>
+    <row r="87" ht="14" customHeight="1"/>
+    <row r="88" ht="14" customHeight="1"/>
+    <row r="89" ht="14" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="72">
+  <mergeCells count="107">
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="A81:M81"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B70:G79"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B50:B51"/>
     <mergeCell ref="F54:G54"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="E80:M80"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="I35:M36"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="F65:G65"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="E65:M65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="H62:H64"/>
     <mergeCell ref="I26:M26"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="F59:G59"/>
+    <mergeCell ref="L78:M78"/>
     <mergeCell ref="F55:G55"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C65:D65"/>
     <mergeCell ref="I34:L34"/>
-    <mergeCell ref="L42:M42"/>
     <mergeCell ref="F51:G51"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="L62:M62"/>
-    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="L71:M71"/>
     <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="B60:G64"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="I35:M36"/>
     <mergeCell ref="L55:M55"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="H59:H61"/>
     <mergeCell ref="L64:M64"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="L73:M73"/>
     <mergeCell ref="L51:M51"/>
-    <mergeCell ref="H53:H55"/>
-    <mergeCell ref="L58:M58"/>
     <mergeCell ref="L54:M54"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L50:M50"/>
     <mergeCell ref="L63:M63"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="L41:M41"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="F56:G56"/>
     <mergeCell ref="F58:G58"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="L40:M40"/>
     <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="L56:M56"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B47:M47"/>
-    <mergeCell ref="L52:M52"/>
     <mergeCell ref="H56:H58"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="F60:G60"/>
     <mergeCell ref="A4:A46"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="L49:M49"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="F53:G53"/>
   </mergeCells>
   <dataValidations count="5">
@@ -1905,16 +2160,19 @@
     <dataValidation sqref="J40:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D50:D59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D50:D69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="J50:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J50:J79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="47" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -1924,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -3355,11 +3613,14 @@
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="15" t="n"/>
-      <c r="B60" s="21" t="inlineStr">
-        <is>
-          <t>팀 핸디는 팀원 핸디 칸의 합계로 적용됩니다. 베이커는 여성 1명 +3, 2명 이상 +5 (한 명 칸에 적어도 됨). 비워 두면 대회에서 규정대로 적용.</t>
-        </is>
-      </c>
+      <c r="B60" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="11" t="n"/>
@@ -3369,6 +3630,12 @@
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="15" t="n"/>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="15" t="n"/>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="11" t="n"/>
@@ -3378,6 +3645,14 @@
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="15" t="n"/>
+      <c r="B62" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="15" t="n"/>
       <c r="H62" s="10" t="n">
         <v>5</v>
       </c>
@@ -3389,6 +3664,12 @@
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="15" t="n"/>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="11" t="n"/>
@@ -3398,6 +3679,14 @@
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="15" t="n"/>
+      <c r="B64" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="11" t="n"/>
@@ -3406,106 +3695,330 @@
       <c r="M64" s="15" t="n"/>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="15" t="n"/>
+      <c r="H65" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="15" t="n"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="15" t="n"/>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="11" t="n"/>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="15" t="n"/>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="15" t="n"/>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="11" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="15" t="n"/>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="11" t="n"/>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="15" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="15" t="n"/>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="15" t="n"/>
+      <c r="B70" s="21" t="inlineStr">
+        <is>
+          <t>팀 핸디는 팀원 핸디 칸의 합계로 적용됩니다. 베이커는 여성 1명 +3, 2명 이상 +5 (한 명 칸에 적어도 됨). 비워 두면 대회에서 규정대로 적용.</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="4" t="n"/>
+      <c r="J70" s="11" t="n"/>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="15" t="n"/>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="15" t="n"/>
+      <c r="H71" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="15" t="n"/>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="15" t="n"/>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="11" t="n"/>
+      <c r="K72" s="11" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="15" t="n"/>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="15" t="n"/>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="11" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="15" t="n"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="15" t="n"/>
+      <c r="H74" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="11" t="n"/>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="15" t="n"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="15" t="n"/>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="15" t="n"/>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="11" t="n"/>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="15" t="n"/>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="15" t="n"/>
+      <c r="H77" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="15" t="n"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="15" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="4" t="n"/>
+      <c r="J78" s="11" t="n"/>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="15" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="15" t="n"/>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="11" t="n"/>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="15" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>총금액</t>
         </is>
       </c>
-      <c r="C65" s="20">
+      <c r="C80" s="20">
         <f>M34</f>
         <v/>
       </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="25" t="inlineStr">
         <is>
           <t>입금계좌 : (대회 공지의 계좌)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="26" t="inlineStr">
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>위와 같이 제46회 네이버 볼링 동호회 서울 전국대회 참가를 신청합니다.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1"/>
-    <row r="68" ht="14" customHeight="1"/>
-    <row r="69" ht="14" customHeight="1"/>
+    <row r="82" ht="14" customHeight="1"/>
+    <row r="83" ht="14" customHeight="1"/>
+    <row r="84" ht="14" customHeight="1"/>
+    <row r="85" ht="14" customHeight="1"/>
+    <row r="86" ht="14" customHeight="1"/>
+    <row r="87" ht="14" customHeight="1"/>
+    <row r="88" ht="14" customHeight="1"/>
+    <row r="89" ht="14" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="72">
+  <mergeCells count="107">
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="A81:M81"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B70:G79"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B50:B51"/>
     <mergeCell ref="F54:G54"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="E80:M80"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="I35:M36"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="F65:G65"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="E65:M65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="H62:H64"/>
     <mergeCell ref="I26:M26"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="F59:G59"/>
+    <mergeCell ref="L78:M78"/>
     <mergeCell ref="F55:G55"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C65:D65"/>
     <mergeCell ref="I34:L34"/>
-    <mergeCell ref="L42:M42"/>
     <mergeCell ref="F51:G51"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="L62:M62"/>
-    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="L71:M71"/>
     <mergeCell ref="I28:J28"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="B60:G64"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="I35:M36"/>
     <mergeCell ref="L55:M55"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="H59:H61"/>
     <mergeCell ref="L64:M64"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="L73:M73"/>
     <mergeCell ref="L51:M51"/>
-    <mergeCell ref="H53:H55"/>
-    <mergeCell ref="L58:M58"/>
     <mergeCell ref="L54:M54"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="L50:M50"/>
     <mergeCell ref="L63:M63"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="L41:M41"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="F56:G56"/>
     <mergeCell ref="F58:G58"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="L40:M40"/>
     <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="L56:M56"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B47:M47"/>
-    <mergeCell ref="L52:M52"/>
     <mergeCell ref="H56:H58"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="F60:G60"/>
     <mergeCell ref="A4:A46"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="L49:M49"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="F53:G53"/>
   </mergeCells>
   <dataValidations count="5">
@@ -3518,15 +4031,18 @@
     <dataValidation sqref="J40:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="D50:D59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D50:D69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
-    <dataValidation sqref="J50:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J50:J79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="47" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>